--- a/project/excel/iso27001.xlsx
+++ b/project/excel/iso27001.xlsx
@@ -7,39 +7,41 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="InformationSecurityManagementSystem" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Organization" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="InterestedParty" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="InformationSecurityPolicy" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TopicSpecificPolicy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Role" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="InformationSecurityObjective" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="RiskAssessmentProcess" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="RiskAssessment" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Risk" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="RiskTreatmentProcess" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="RiskTreatmentPlan" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="StatementOfApplicability" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="SoAEntry" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="SecurityControl" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Resource" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="CompetenceRecord" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="AwarenessProgram" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="CommunicationPlan" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="CommunicationItem" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="OperationalProcedure" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="MonitoringProgram" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="MonitoringItem" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="InternalAudit" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="AuditProgramme" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="AuditFinding" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="ManagementReview" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Nonconformity" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="CorrectiveAction" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="ImprovementOpportunity" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Asset" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="InformationSecurityEvent" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="InformationSecurityIncident" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="IsmsManagementSystem" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="IsmsOrganization" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IsmsInterestedParty" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IsmsPolicy" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IsmsTopicSpecificPolicy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="IsmsRole" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="IsmsObjective" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="IsmsRiskAssessmentProcess" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="IsmsRiskAssessment" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="IsmsRisk" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="IsmsRiskTreatmentProcess" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="IsmsRiskTreatmentPlan" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IsmsStatementOfApplicability" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="IsmsIncludedControl" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="IsmsExcludedControl" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="IsmsControl" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="IsmsAsset" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="IsmsResource" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="IsmsCompetenceRecord" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="IsmsAwarenessProgramme" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="IsmsCommunicationPlan" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="IsmsCommunication" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="IsmsDocumentedInformation" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="IsmsOperationalProcedure" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="IsmsMonitoringProgramme" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="IsmsMonitoringItem" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="IsmsAuditProgramme" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="IsmsAudit" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="IsmsAuditFinding" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="IsmsManagementReview" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="IsmsNonconformity" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="IsmsCorrectiveAction" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="IsmsImprovementOpportunity" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="IsmsSecurityEvent" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="IsmsSecurityIncident" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,238 +447,248 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>isms_organization</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>top_management</t>
+          <t>isms_top_management</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>governing_body</t>
+          <t>isms_governing_body</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>leadership_commitment_evidence</t>
+          <t>isms_leadership_evidence</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>scope_statement</t>
+          <t>isms_scope</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>scope_boundaries</t>
+          <t>isms_scope_boundaries</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>scope_exclusions</t>
+          <t>isms_scope_exclusions</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>interfaces_and_dependencies</t>
+          <t>isms_interfaces</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>processes_and_interactions</t>
+          <t>isms_processes</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>context_internal_issues</t>
+          <t>isms_internal_issues</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>context_external_issues</t>
+          <t>isms_external_issues</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>interested_parties</t>
+          <t>isms_risk_and_opportunity_actions</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>information_security_policy</t>
+          <t>isms_planned_changes</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>objectives</t>
+          <t>isms_external_services</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>risks_and_opportunities_actions</t>
+          <t>isms_certification_status</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>planned_changes</t>
+          <t>isms_certification_body</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>externally_provided_services</t>
+          <t>isms_certification_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>risk_assessment_process</t>
+          <t>isms_recertification_date</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>risk_treatment_process</t>
+          <t>isms_interested_parties</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>statement_of_applicability</t>
+          <t>isms_policy</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>controls</t>
+          <t>isms_topic_specific_policies</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>isms_roles</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>isms_objectives</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>competence_records</t>
+          <t>isms_risk_assessment_process</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>awareness_program</t>
+          <t>isms_risk_treatment_process</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>communication_plan</t>
+          <t>isms_risk_assessments</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>documented_information_register</t>
+          <t>isms_risks</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>operational_procedures</t>
+          <t>isms_risk_treatment_plans</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>risk_assessments</t>
+          <t>isms_statement_of_applicability</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>risk_treatment_plans</t>
+          <t>isms_controls</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>monitoring_program</t>
+          <t>isms_assets</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>internal_audits</t>
+          <t>isms_resources</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>management_reviews</t>
+          <t>isms_competence_records</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>nonconformities</t>
+          <t>isms_awareness_programme</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>corrective_actions</t>
+          <t>isms_communication_plan</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>improvements</t>
+          <t>isms_documented_information</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>certification_status</t>
+          <t>isms_operational_procedures</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>certification_body</t>
+          <t>isms_monitoring_programme</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>certification_date</t>
+          <t>isms_audit_programmes</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>recertification_date</t>
+          <t>isms_audits</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_management_reviews</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>isms_nonconformities</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>isms_corrective_actions</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>isms_improvements</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>isms_security_events</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -691,33 +703,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>affected_assets</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>affected_security_properties</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>risk_source</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>threat_description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>vulnerability_description</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>affected_assets</t>
+          <t>risk_threat</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>affected_cia_properties</t>
+          <t>risk_vulnerability</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -727,27 +739,27 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>likelihood</t>
+          <t>risk_likelihood</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>risk_impact</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>inherent_risk_level</t>
+          <t>risk_inherent_level</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>existing_controls</t>
+          <t>risk_existing_controls</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>residual_risk_level</t>
+          <t>risk_residual_level</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -757,48 +769,28 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>treatment_priority</t>
+          <t>risk_treatment_priority</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>related_treatment_plan</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"confidentiality,integrity,availability"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -814,7 +806,7 @@
       <formula1>"very_low,low,medium,high,critical"</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"modify,accept,avoid,share"</formula1>
+      <formula1>"modify,retain,avoid,share"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -827,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -838,141 +830,126 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>control_selection_criteria</t>
+          <t>treatment_control_selection</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>annex_a_omission_verification</t>
+          <t>treatment_annex_a_comparison</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>soa_template</t>
+          <t>treatment_soa_template</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>approval_workflow</t>
+          <t>treatment_approval_workflow</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -983,183 +960,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>implementation_state</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>plan_scope</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>risks_addressed</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>treatment_actions</t>
+          <t>plan_risks</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>controls_to_implement</t>
+          <t>plan_actions</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>resources_required</t>
+          <t>plan_controls</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>responsible_parties</t>
+          <t>plan_resources</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>implementation_timeline</t>
+          <t>plan_responsible_parties</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>risk_owner_approval</t>
+          <t>plan_timeline</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>plan_risk_owner_approval</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>residual_risk_acceptance</t>
+          <t>plan_residual_risk_acceptance</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>implementation_status</t>
+          <t>plan_completion_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>completion_date</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"not_started,planned,in_progress,implemented,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"not_started,planned,in_progress,implemented"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1172,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1183,146 +1147,106 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>total_controls</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>implemented_count</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>planned_count</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>not_applicable_count</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>last_review_date</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>title</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1339,49 +1263,49 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>control_reference</t>
+          <t>implementation_state</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>is_applicable</t>
+          <t>responsible_role</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>inclusion_justification</t>
+          <t>included_control</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>exclusion_justification</t>
+          <t>included_evidence</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>implementation_status</t>
+          <t>included_target_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>implementation_evidence</t>
+          <t>entry_annex_a_control</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>responsible_role</t>
+          <t>entry_type</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>target_implementation_date</t>
+          <t>entry_justification</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"not_started,planned,in_progress,implemented,not_applicable"</formula1>
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"not_started,planned,in_progress,implemented"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1394,120 +1318,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>control_id</t>
+          <t>entry_annex_a_control</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>control_title</t>
+          <t>entry_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>control_category</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>control_text</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>implementation_guidance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>related_controls</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>applicable_threats</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>applicable_assets</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>control_owner</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>implementation_status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>implementation_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>effectiveness_rating</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>last_test_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>evidence_references</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>entry_justification</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"organizational,people,physical,technological"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"not_started,planned,in_progress,implemented,not_applicable"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1518,72 +1349,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>resource_type</t>
+          <t>relevant_controls</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>implementation_state</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>allocation_date</t>
+          <t>control_annex_a_controls</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>allocated_to</t>
+          <t>control_theme</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>control_text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>availability_status</t>
+          <t>control_guidance</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>control_threats</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>control_asset_types</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>control_owner</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>control_implementation_date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>control_effectiveness</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>control_last_tested</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>control_evidence</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"not_started,planned,in_progress,implemented"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"organizational,people,physical,technological"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1594,172 +1453,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>relevant_controls</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>person_role</t>
+          <t>asset_category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>required_competencies</t>
+          <t>asset_owner</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>education_records</t>
+          <t>asset_custodian</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>training_records</t>
+          <t>asset_classification</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>experience_records</t>
+          <t>asset_location</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>competency_assessment_date</t>
+          <t>asset_criticality</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>competency_gaps</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>development_actions</t>
+          <t>title</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>document_type</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>document_reference</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>approved_by</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1770,157 +1519,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>awareness_topics</t>
+          <t>resource_category</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>delivery_methods</t>
+          <t>resource_quantity</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>resource_allocation_date</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>resource_allocated_to</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>completion_tracking</t>
+          <t>resource_cost</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>effectiveness_measures</t>
+          <t>resource_availability</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>approved_by</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1931,132 +1580,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>communication_items</t>
+          <t>competence_person</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>competence_role</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>competence_required</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>competence_education</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>competence_training</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>competence_experience</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>competence_assessment_date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>competence_gaps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>competence_actions</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>approved_by</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2067,93 +1741,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>legal_name</t>
+          <t>organization_legal_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>trading_names</t>
+          <t>organization_trading_names</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>organization_type</t>
+          <t>organization_kind</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>industry_sector</t>
+          <t>organization_sector</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>size_category</t>
+          <t>organization_size</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>employee_count</t>
+          <t>organization_employee_count</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>geographic_locations</t>
+          <t>organization_locations</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>regulatory_jurisdictions</t>
+          <t>organization_jurisdictions</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>parent_organization</t>
+          <t>organization_parent</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>subsidiaries</t>
+          <t>organization_subsidiaries</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>climate_change_relevant</t>
+          <t>organization_climate_change_relevant</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -2168,43 +1827,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>awareness_topics</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>awareness_methods</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>awareness_audience</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>awareness_frequency</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>awareness_completion_tracking</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>responsible_party</t>
+          <t>awareness_effectiveness</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>records_required</t>
+          <t>document_reference</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>document_version</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>document_author</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>document_owner</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>document_approver</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>document_approval_date</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>document_effective_date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>document_last_review_date</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>document_next_review_date</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
@@ -2219,157 +1973,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>procedure_scope</t>
+          <t>communication_items</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>process_criteria</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>control_measures</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>responsible_roles</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>related_controls</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>change_control_requirements</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>title</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2380,132 +2094,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>monitoring_items</t>
+          <t>responsible_role</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>communication_subject</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>communication_purpose</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>communication_audience</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>communication_frequency</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>communication_method</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>communication_records_required</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2516,67 +2145,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>metric_name</t>
+          <t>document_kind</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>metric_description</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>measurement_method</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>measurement_frequency</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>responsible_party</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>analysis_frequency</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>analyst</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>target_threshold</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alert_threshold</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>current_value</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>trend</t>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"procedure,standard,guideline,record,plan,report"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2587,210 +2271,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>audit_reference</t>
+          <t>relevant_controls</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>audit_type</t>
+          <t>procedure_scope</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>audit_scope</t>
+          <t>procedure_criteria</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>audit_criteria</t>
+          <t>procedure_control_measures</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>audit_objectives</t>
+          <t>procedure_roles</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>audit_period_start</t>
+          <t>procedure_change_control</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>audit_period_end</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>lead_auditor</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>audit_team</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>auditee_representatives</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>audit_plan</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>findings</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>positive_observations</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>audit_conclusion</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>report_date</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>report_distribution</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>title</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"internal,external_second_party,external_third_party,surveillance,recertification,combined"</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q2:Q1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2801,157 +2417,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>programme_period</t>
+          <t>monitoring_items</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>planned_audits</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>audit_frequency_rationale</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>resource_requirements</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>auditor_qualifications</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>programme_status</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>title</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2962,98 +2538,494 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>responsible_role</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>monitoring_metric</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>monitoring_description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>monitoring_method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monitoring_frequency</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>monitoring_analysis_frequency</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monitoring_analyst</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>monitoring_target</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monitoring_alert_threshold</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>monitoring_current_value</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>monitoring_trend</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>programme_period</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>programme_audits</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>programme_frequency_rationale</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>programme_resources</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>programme_auditor_qualifications</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>programme_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>document_reference</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>document_version</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>document_author</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>document_owner</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>document_approver</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>document_approval_date</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>document_effective_date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>document_last_review_date</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>document_next_review_date</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AI1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>audit_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>audit_standards</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>audit_scope</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>audit_criteria</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>audit_objectives</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>audit_period_start</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>audit_period_end</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>audit_lead</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>audit_team</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>audit_auditees</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>audit_plan</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>audit_findings</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>audit_conclusion</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>audit_report_date</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>audit_report_distribution</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>document_reference</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>document_version</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>document_author</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>document_owner</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>document_approver</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_approval_date</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>document_effective_date</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>document_last_review_date</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>document_next_review_date</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"first_party,second_party,third_party"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"iso_iec_27001,iso_iec_27701,iso_iec_42001,iso_9001,iso_14001,iso_22301,iso_iec_20000_1"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>finding_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>clause_reference</t>
+          <t>finding_requirement</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>control_reference</t>
+          <t>finding_control</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>finding_description</t>
+          <t>finding_evidence</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>objective_evidence</t>
+          <t>finding_root_cause</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>root_cause_analysis</t>
+          <t>finding_risk</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>risk_implication</t>
+          <t>finding_recommendation</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>recommended_action</t>
+          <t>finding_auditee_response</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>auditee_response</t>
+          <t>finding_corrective_action</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>linked_corrective_action</t>
+          <t>finding_closure_status</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>closure_status</t>
+          <t>finding_closure_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>closure_date</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -3067,497 +3039,64 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AJ1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>attendees</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>previous_actions_status</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>context_changes</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>interested_party_changes</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>interested_party_feedback</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>performance_trends</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>audit_results_summary</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>risk_assessment_results</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>risk_treatment_status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>risks_and_opportunities_changes</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>improvement_opportunities</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>decisions</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>action_items</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>next_review_date</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>document_type</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>document_reference</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>approved_by</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nonconformity_source</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>detection_date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>detected_by</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>requirement_violated</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>nonconformity_description</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>immediate_actions</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>consequences_addressed</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>root_cause</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>similar_nonconformities_check</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>linked_corrective_actions</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>closure_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>closure_evidence</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>linked_nonconformity</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>action_description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>root_cause_addressed</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>responsible_party</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>target_completion_date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>actual_completion_date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>resources_required</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>effectiveness_criteria</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>effectiveness_review_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>effectiveness_verified</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>isms_changes_required</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>party_type</t>
+          <t>party_category</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>relationship</t>
+          <t>party_relationship</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>requirements</t>
+          <t>party_requirements</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>addressed_requirements</t>
+          <t>party_addressed_requirements</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>climate_change_related_requirements</t>
+          <t>party_climate_change_requirements</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>communication_needs</t>
+          <t>party_communication_needs</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>party_contact</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -3572,98 +3111,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>improvement_source</t>
+          <t>review_held_on</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>identification_date</t>
+          <t>review_attendees</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>identified_by</t>
+          <t>review_previous_actions</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>improvement_description</t>
+          <t>review_context_changes</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>expected_benefit</t>
+          <t>review_interested_party_changes</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>review_interested_party_feedback</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>implementation_plan</t>
+          <t>review_performance_trends</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>responsible_party</t>
+          <t>review_audit_results</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>target_date</t>
+          <t>review_risk_assessment_results</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>actual_completion_date</t>
+          <t>review_risk_treatment_status</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>outcome_assessment</t>
+          <t>review_risks_and_opportunities</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>review_improvement_opportunities</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>review_decisions</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>review_actions</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>review_next_date</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>document_reference</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>document_version</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>document_author</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>document_owner</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>document_approver</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_approval_date</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>document_effective_date</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>document_last_review_date</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>document_next_review_date</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -3684,72 +3308,72 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>asset_type</t>
+          <t>nonconformity_source</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>asset_owner</t>
+          <t>nonconformity_detected_on</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>asset_custodian</t>
+          <t>nonconformity_detected_by</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>nonconformity_requirement</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>nonconformity_immediate_actions</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>criticality</t>
+          <t>nonconformity_consequences</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>related_risks</t>
+          <t>nonconformity_root_cause</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>applicable_controls</t>
+          <t>nonconformity_similar_check</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>nonconformity_status</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nonconformity_closure_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>nonconformity_closure_evidence</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -3764,73 +3388,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>event_datetime</t>
+          <t>responsible_role</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>reporter</t>
+          <t>action_nonconformities</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>event_description</t>
+          <t>action_root_cause</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>affected_assets</t>
+          <t>action_target_date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>initial_assessment</t>
+          <t>action_completion_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>categorized_as_incident</t>
+          <t>action_resources</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>linked_incident</t>
+          <t>action_effectiveness_criteria</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>action_effectiveness_review_date</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>action_effective</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>action_isms_changes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>action_status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -3845,138 +3474,275 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>incident_datetime</t>
+          <t>responsible_role</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>improvement_source</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>improvement_identified_on</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>improvement_identified_by</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>improvement_benefit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>improvement_priority</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>improvement_plan</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>improvement_target_date</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>improvement_completion_date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>improvement_outcome</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>improvement_status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>affected_assets</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>event_occurred_at</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>event_reporter</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>event_assessment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>affected_security_properties</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>incident_category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>incident_severity</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>incident_detection_method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>incident_response_actions</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>incident_containment_actions</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>incident_eradication_actions</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>incident_recovery_actions</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>incident_root_cause</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>incident_lessons_learned</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>incident_evidence</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>incident_notification_required</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>incident_notifications</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>incident_closed_at</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>incident_review</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>affected_assets</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>affected_cia</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>incident_description</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>detection_method</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>response_actions</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>containment_actions</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>eradication_actions</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>recovery_actions</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>root_cause</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>lessons_learned</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>evidence_collected</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>notification_required</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>notifications_made</t>
-        </is>
-      </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>closure_datetime</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>post_incident_review</t>
+          <t>event_occurred_at</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>event_reporter</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>event_assessment</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"confidentiality,integrity,availability"</formula1>
+    </dataValidation>
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"very_low,low,medium,high,critical"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"confidentiality,integrity,availability"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3989,7 +3755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4005,162 +3771,134 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>commitment_statements</t>
+          <t>policy_commitments</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>applicability_statement</t>
+          <t>policy_applicability</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>communication_date</t>
+          <t>policy_communication_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>acknowledgment_required</t>
+          <t>policy_acknowledgement_required</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>last_policy_review_date</t>
+          <t>policy_management_systems</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>next_policy_review_date</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>related_topic_policies</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>integrated_management_systems</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>title</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"iso_iec_27001,iso_iec_27701,iso_iec_27017,iso_iec_27018,iso_iec_42001,iso_9001,iso_14001,iso_22301,iso_iec_20000_1,iso_31000"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"iso_iec_27001,iso_iec_27701,iso_iec_42001,iso_9001,iso_14001,iso_22301,iso_iec_20000_1"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4173,147 +3911,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>topic_area</t>
+          <t>relevant_controls</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>parent_policy</t>
+          <t>topic_policy_topic</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>applicable_controls</t>
+          <t>topic_policy_parent</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>topic_policy_audience</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4324,73 +4047,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>role_type</t>
+          <t>role_category</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>responsibilities</t>
+          <t>role_responsibilities</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>authorities</t>
+          <t>role_authorities</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>accountability</t>
+          <t>role_accountability</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>role_holders</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>delegation_rules</t>
+          <t>role_delegation</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>reporting_line</t>
+          <t>role_reports_to</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -4405,103 +4113,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>responsible_role</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>relevant_controls</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>objective_statement</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>target_value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>current_value</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>metric_definition</t>
+          <t>objective_target</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>measurement_method</t>
+          <t>objective_current_value</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>measurement_frequency</t>
+          <t>objective_metric</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>responsible_role</t>
+          <t>objective_measurement_method</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>target_date</t>
+          <t>objective_measurement_frequency</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>achievement_status</t>
+          <t>objective_target_date</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>related_risks</t>
+          <t>objective_achievement</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>related_controls</t>
+          <t>objective_risks</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>action_plan</t>
+          <t>objective_action_plan</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>objective_resources_required</t>
+          <t>objective_resources</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4527,22 +4220,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>assessment_criteria</t>
+          <t>risk_assessment_criteria</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>assessment_methodology</t>
+          <t>risk_assessment_method</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>likelihood_scale</t>
+          <t>risk_likelihood_scale</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>impact_scale</t>
+          <t>risk_impact_scale</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -4552,131 +4245,116 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>assessment_frequency</t>
+          <t>risk_assessment_frequency</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>trigger_events</t>
+          <t>risk_assessment_triggers</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4687,7 +4365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4703,151 +4381,136 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>assessor</t>
+          <t>assessment_assessor</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>methodology_used</t>
+          <t>assessment_method_used</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>risks_identified</t>
+          <t>assessment_risks</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>summary_findings</t>
+          <t>assessment_summary</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>recommendations</t>
+          <t>assessment_recommendations</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>next_assessment_date</t>
+          <t>assessment_next_date</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_external_source</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/project/excel/iso27001.xlsx
+++ b/project/excel/iso27001.xlsx
@@ -850,102 +850,102 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -1021,102 +1021,102 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -1147,102 +1147,102 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -1631,102 +1631,102 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -1863,102 +1863,102 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -1984,102 +1984,102 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -2156,102 +2156,102 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -2307,102 +2307,102 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -2428,102 +2428,102 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -2645,102 +2645,102 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -2836,102 +2836,102 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -3192,102 +3192,102 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -3796,102 +3796,102 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -3937,102 +3937,102 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -4255,102 +4255,102 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
@@ -4411,102 +4411,102 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>document_version</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>document_author</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>document_owner</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>document_approver</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>document_approval_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>document_effective_date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>document_last_review_date</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>document_next_review_date</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>document_status</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>document_classification</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>document_retention</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>document_distribution</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>document_storage</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>document_change_control</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>document_external_origin</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>document_external_source</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>isms_id</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>

--- a/project/excel/iso27001.xlsx
+++ b/project/excel/iso27001.xlsx
@@ -7,39 +7,41 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="InformationSecurityManagementSystem" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Organization" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="InterestedParty" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="InformationSecurityPolicy" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="TopicSpecificPolicy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Role" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="InformationSecurityObjective" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="RiskAssessmentProcess" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="RiskAssessment" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Risk" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="RiskTreatmentProcess" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="RiskTreatmentPlan" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="StatementOfApplicability" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="SoAEntry" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="SecurityControl" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Resource" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="CompetenceRecord" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="AwarenessProgram" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="CommunicationPlan" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="CommunicationItem" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="OperationalProcedure" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="MonitoringProgram" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="MonitoringItem" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="InternalAudit" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="AuditProgramme" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="AuditFinding" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="ManagementReview" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Nonconformity" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="CorrectiveAction" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="ImprovementOpportunity" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Asset" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="InformationSecurityEvent" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="InformationSecurityIncident" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="IsmsManagementSystem" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="IsmsOrganization" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IsmsInterestedParty" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IsmsPolicy" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IsmsTopicSpecificPolicy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="IsmsRole" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="IsmsObjective" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="IsmsRiskAssessmentProcess" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="IsmsRiskAssessment" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="IsmsRisk" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="IsmsRiskTreatmentProcess" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="IsmsRiskTreatmentPlan" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IsmsStatementOfApplicability" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="IsmsIncludedControl" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="IsmsExcludedControl" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="IsmsControl" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="IsmsAsset" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="IsmsResource" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="IsmsCompetenceRecord" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="IsmsAwarenessProgramme" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="IsmsCommunicationPlan" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="IsmsCommunication" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="IsmsDocumentedInformation" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="IsmsOperationalProcedure" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="IsmsMonitoringProgramme" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="IsmsMonitoringItem" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="IsmsAuditProgramme" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="IsmsAudit" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="IsmsAuditFinding" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="IsmsManagementReview" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="IsmsNonconformity" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="IsmsCorrectiveAction" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="IsmsImprovementOpportunity" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="IsmsSecurityEvent" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="IsmsSecurityIncident" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,238 +447,248 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>isms_organization</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>top_management</t>
+          <t>isms_top_management</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>governing_body</t>
+          <t>isms_governing_body</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>leadership_commitment_evidence</t>
+          <t>isms_leadership_evidence</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>scope_statement</t>
+          <t>isms_scope</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>scope_boundaries</t>
+          <t>isms_scope_boundaries</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>scope_exclusions</t>
+          <t>isms_scope_exclusions</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>interfaces_and_dependencies</t>
+          <t>isms_interfaces</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>processes_and_interactions</t>
+          <t>isms_processes</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>context_internal_issues</t>
+          <t>isms_internal_issues</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>context_external_issues</t>
+          <t>isms_external_issues</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>interested_parties</t>
+          <t>isms_risk_and_opportunity_actions</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>information_security_policy</t>
+          <t>isms_planned_changes</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>objectives</t>
+          <t>isms_external_services</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>risks_and_opportunities_actions</t>
+          <t>isms_certification_status</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>planned_changes</t>
+          <t>isms_certification_body</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>externally_provided_services</t>
+          <t>isms_certification_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>risk_assessment_process</t>
+          <t>isms_recertification_date</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>risk_treatment_process</t>
+          <t>isms_interested_parties</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>statement_of_applicability</t>
+          <t>isms_policy</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>controls</t>
+          <t>isms_topic_specific_policies</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>roles</t>
+          <t>isms_roles</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>isms_objectives</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>competence_records</t>
+          <t>isms_risk_assessment_process</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>awareness_program</t>
+          <t>isms_risk_treatment_process</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>communication_plan</t>
+          <t>isms_risk_assessments</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>documented_information_register</t>
+          <t>isms_risks</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>operational_procedures</t>
+          <t>isms_risk_treatment_plans</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>risk_assessments</t>
+          <t>isms_statement_of_applicability</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>risk_treatment_plans</t>
+          <t>isms_controls</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>monitoring_program</t>
+          <t>isms_assets</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>internal_audits</t>
+          <t>isms_resources</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>management_reviews</t>
+          <t>isms_competence_records</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>nonconformities</t>
+          <t>isms_awareness_programme</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>corrective_actions</t>
+          <t>isms_communication_plan</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>improvements</t>
+          <t>isms_documented_information</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>certification_status</t>
+          <t>isms_operational_procedures</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>certification_body</t>
+          <t>isms_monitoring_programme</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>certification_date</t>
+          <t>isms_audit_programmes</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>recertification_date</t>
+          <t>isms_audits</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_management_reviews</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>isms_nonconformities</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>isms_corrective_actions</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>isms_improvements</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>isms_security_events</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -691,33 +703,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>affected_assets</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>affected_security_properties</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>risk_source</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>threat_description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>vulnerability_description</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>affected_assets</t>
+          <t>risk_threat</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>affected_cia_properties</t>
+          <t>risk_vulnerability</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -727,27 +739,27 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>likelihood</t>
+          <t>risk_likelihood</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>risk_impact</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>inherent_risk_level</t>
+          <t>risk_inherent_level</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>existing_controls</t>
+          <t>risk_existing_controls</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>residual_risk_level</t>
+          <t>risk_residual_level</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -757,48 +769,28 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>treatment_priority</t>
+          <t>risk_treatment_priority</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>related_treatment_plan</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"confidentiality,integrity,availability"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -814,7 +806,7 @@
       <formula1>"very_low,low,medium,high,critical"</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"modify,accept,avoid,share"</formula1>
+      <formula1>"modify,retain,avoid,share"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -827,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -838,141 +830,126 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>control_selection_criteria</t>
+          <t>treatment_control_selection</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>annex_a_omission_verification</t>
+          <t>treatment_annex_a_comparison</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>soa_template</t>
+          <t>treatment_soa_template</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>approval_workflow</t>
+          <t>treatment_approval_workflow</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -983,183 +960,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>implementation_state</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>plan_scope</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>risks_addressed</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>treatment_actions</t>
+          <t>plan_risks</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>controls_to_implement</t>
+          <t>plan_actions</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>resources_required</t>
+          <t>plan_controls</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>responsible_parties</t>
+          <t>plan_resources</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>implementation_timeline</t>
+          <t>plan_responsible_parties</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>risk_owner_approval</t>
+          <t>plan_timeline</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>plan_risk_owner_approval</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>residual_risk_acceptance</t>
+          <t>plan_residual_risk_acceptance</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>implementation_status</t>
+          <t>plan_completion_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>completion_date</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>title</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"not_started,planned,in_progress,implemented,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"not_started,planned,in_progress,implemented"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1172,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1183,146 +1147,106 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>total_controls</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>implemented_count</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>planned_count</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>not_applicable_count</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>last_review_date</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1339,49 +1263,49 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>control_reference</t>
+          <t>implementation_state</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>is_applicable</t>
+          <t>responsible_role</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>inclusion_justification</t>
+          <t>included_control</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>exclusion_justification</t>
+          <t>included_evidence</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>implementation_status</t>
+          <t>included_target_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>implementation_evidence</t>
+          <t>entry_annex_a_control</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>responsible_role</t>
+          <t>entry_type</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>target_implementation_date</t>
+          <t>entry_justification</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"not_started,planned,in_progress,implemented,not_applicable"</formula1>
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"not_started,planned,in_progress,implemented"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1394,120 +1318,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>control_id</t>
+          <t>entry_annex_a_control</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>control_title</t>
+          <t>entry_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>control_category</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>control_text</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>implementation_guidance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>related_controls</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>applicable_threats</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>applicable_assets</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>control_owner</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>implementation_status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>implementation_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>effectiveness_rating</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>last_test_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>evidence_references</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>entry_justification</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"organizational,people,physical,technological"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"not_started,planned,in_progress,implemented,not_applicable"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1518,72 +1349,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>resource_type</t>
+          <t>relevant_controls</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>implementation_state</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>allocation_date</t>
+          <t>control_annex_a_controls</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>allocated_to</t>
+          <t>control_theme</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>control_text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>availability_status</t>
+          <t>control_guidance</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>control_threats</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>control_asset_types</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>control_owner</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>control_implementation_date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>control_effectiveness</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>control_last_tested</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>control_evidence</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"not_started,planned,in_progress,implemented"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"organizational,people,physical,technological"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1594,172 +1453,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>person_name</t>
+          <t>relevant_controls</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>person_role</t>
+          <t>asset_category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>required_competencies</t>
+          <t>asset_owner</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>education_records</t>
+          <t>asset_custodian</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>training_records</t>
+          <t>asset_classification</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>experience_records</t>
+          <t>asset_location</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>competency_assessment_date</t>
+          <t>asset_criticality</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>competency_gaps</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>development_actions</t>
+          <t>title</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>document_type</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>document_reference</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>approved_by</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1770,157 +1519,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>awareness_topics</t>
+          <t>resource_category</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>delivery_methods</t>
+          <t>resource_quantity</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>resource_allocation_date</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>resource_allocated_to</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>completion_tracking</t>
+          <t>resource_cost</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>effectiveness_measures</t>
+          <t>resource_availability</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>approved_by</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1931,132 +1580,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>communication_items</t>
+          <t>competence_person</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>competence_role</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>competence_required</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>competence_education</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>competence_training</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>competence_experience</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>competence_assessment_date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>competence_gaps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>competence_actions</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>approved_by</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>created_date</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>modified_date</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>version</t>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2067,93 +1741,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>legal_name</t>
+          <t>organization_legal_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>trading_names</t>
+          <t>organization_trading_names</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>organization_type</t>
+          <t>organization_kind</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>industry_sector</t>
+          <t>organization_sector</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>size_category</t>
+          <t>organization_size</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>employee_count</t>
+          <t>organization_employee_count</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>geographic_locations</t>
+          <t>organization_locations</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>regulatory_jurisdictions</t>
+          <t>organization_jurisdictions</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>parent_organization</t>
+          <t>organization_parent</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>subsidiaries</t>
+          <t>organization_subsidiaries</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>climate_change_relevant</t>
+          <t>organization_climate_change_relevant</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -2168,43 +1827,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>awareness_topics</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>awareness_methods</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>audience</t>
+          <t>awareness_audience</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>awareness_frequency</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>awareness_completion_tracking</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>responsible_party</t>
+          <t>awareness_effectiveness</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>records_required</t>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>document_reference</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>document_version</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>document_author</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>document_owner</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>document_approver</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>document_approval_date</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>document_effective_date</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>document_last_review_date</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>document_next_review_date</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
@@ -2219,157 +1973,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>procedure_scope</t>
+          <t>communication_items</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>process_criteria</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>control_measures</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>responsible_roles</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>related_controls</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>change_control_requirements</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2380,132 +2094,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>monitoring_items</t>
+          <t>responsible_role</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>communication_subject</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>communication_purpose</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>communication_audience</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>communication_frequency</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>communication_method</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>communication_records_required</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2516,67 +2145,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>metric_name</t>
+          <t>document_kind</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>metric_description</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>measurement_method</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>measurement_frequency</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>responsible_party</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>analysis_frequency</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>analyst</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>target_threshold</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>alert_threshold</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>current_value</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>trend</t>
+          <t>document_effective_date</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>document_last_review_date</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>document_next_review_date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"procedure,standard,guideline,record,plan,report"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2587,210 +2271,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>audit_reference</t>
+          <t>relevant_controls</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>audit_type</t>
+          <t>procedure_scope</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>audit_scope</t>
+          <t>procedure_criteria</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>audit_criteria</t>
+          <t>procedure_control_measures</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>audit_objectives</t>
+          <t>procedure_roles</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>audit_period_start</t>
+          <t>procedure_change_control</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>audit_period_end</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>lead_auditor</t>
+          <t>title</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>audit_team</t>
+          <t>description</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>auditee_representatives</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>audit_plan</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>findings</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>positive_observations</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>audit_conclusion</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>report_date</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>report_distribution</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"internal,external_second_party,external_third_party,surveillance,recertification,combined"</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q2:Q1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2801,157 +2417,117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>programme_period</t>
+          <t>monitoring_items</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>planned_audits</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>audit_frequency_rationale</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>resource_requirements</t>
+          <t>description</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>auditor_qualifications</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>programme_status</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2962,98 +2538,494 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>responsible_role</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>monitoring_metric</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>monitoring_description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>monitoring_method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monitoring_frequency</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>monitoring_analysis_frequency</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monitoring_analyst</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>monitoring_target</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monitoring_alert_threshold</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>monitoring_current_value</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>monitoring_trend</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>programme_period</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>programme_audits</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>programme_frequency_rationale</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>programme_resources</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>programme_auditor_qualifications</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>programme_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>document_reference</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>document_version</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>document_author</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>document_owner</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>document_approver</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>document_approval_date</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>document_effective_date</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>document_last_review_date</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>document_next_review_date</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AI1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>audit_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>audit_standards</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>audit_scope</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>audit_criteria</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>audit_objectives</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>audit_period_start</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>audit_period_end</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>audit_lead</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>audit_team</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>audit_auditees</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>audit_plan</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>audit_findings</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>audit_conclusion</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>audit_report_date</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>audit_report_distribution</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>document_reference</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>document_version</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_author</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>document_owner</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>document_approver</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>document_approval_date</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>document_effective_date</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>document_last_review_date</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>document_next_review_date</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"first_party,second_party,third_party"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"iso_iec_27001,iso_iec_27701,iso_iec_42001,iso_9001,iso_14001,iso_22301,iso_iec_20000_1"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>finding_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>clause_reference</t>
+          <t>finding_requirement</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>control_reference</t>
+          <t>finding_control</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>finding_description</t>
+          <t>finding_evidence</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>objective_evidence</t>
+          <t>finding_root_cause</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>root_cause_analysis</t>
+          <t>finding_risk</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>risk_implication</t>
+          <t>finding_recommendation</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>recommended_action</t>
+          <t>finding_auditee_response</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>auditee_response</t>
+          <t>finding_corrective_action</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>linked_corrective_action</t>
+          <t>finding_closure_status</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>closure_status</t>
+          <t>finding_closure_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>closure_date</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -3067,497 +3039,64 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AJ1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>review_date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>attendees</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>previous_actions_status</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>context_changes</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>interested_party_changes</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>interested_party_feedback</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>performance_trends</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>audit_results_summary</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>risk_assessment_results</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>risk_treatment_status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>risks_and_opportunities_changes</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>improvement_opportunities</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>decisions</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>action_items</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>next_review_date</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>document_type</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>document_reference</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>approved_by</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>approved_date</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>effective_date</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>classification</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>retention_period</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>distribution_controls</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>storage_and_preservation</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>change_control_method</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>external_origin</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>external_origin_source</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nonconformity_source</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>detection_date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>detected_by</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>requirement_violated</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>nonconformity_description</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>immediate_actions</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>consequences_addressed</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>root_cause</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>similar_nonconformities_check</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>linked_corrective_actions</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>closure_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>closure_evidence</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>linked_nonconformity</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>action_description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>root_cause_addressed</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>responsible_party</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>target_completion_date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>actual_completion_date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>resources_required</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>effectiveness_criteria</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>effectiveness_review_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>effectiveness_verified</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>isms_changes_required</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>party_type</t>
+          <t>party_category</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>relationship</t>
+          <t>party_relationship</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>requirements</t>
+          <t>party_requirements</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>addressed_requirements</t>
+          <t>party_addressed_requirements</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>climate_change_related_requirements</t>
+          <t>party_climate_change_requirements</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>communication_needs</t>
+          <t>party_communication_needs</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>contact_information</t>
+          <t>party_contact</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -3572,98 +3111,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>improvement_source</t>
+          <t>review_held_on</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>identification_date</t>
+          <t>review_attendees</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>identified_by</t>
+          <t>review_previous_actions</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>improvement_description</t>
+          <t>review_context_changes</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>expected_benefit</t>
+          <t>review_interested_party_changes</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>review_interested_party_feedback</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>implementation_plan</t>
+          <t>review_performance_trends</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>responsible_party</t>
+          <t>review_audit_results</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>target_date</t>
+          <t>review_risk_assessment_results</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>actual_completion_date</t>
+          <t>review_risk_treatment_status</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>outcome_assessment</t>
+          <t>review_risks_and_opportunities</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>review_improvement_opportunities</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>review_decisions</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>review_actions</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>review_next_date</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>version</t>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>document_reference</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>document_version</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>document_author</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>document_owner</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>document_approver</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>document_approval_date</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>document_effective_date</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>document_last_review_date</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>document_next_review_date</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>document_status</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>document_classification</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>document_retention</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>document_distribution</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>document_storage</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>document_change_control</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>document_external_origin</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
@@ -3684,72 +3308,72 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>asset_type</t>
+          <t>nonconformity_source</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>asset_owner</t>
+          <t>nonconformity_detected_on</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>asset_custodian</t>
+          <t>nonconformity_detected_by</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>nonconformity_requirement</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>nonconformity_immediate_actions</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>criticality</t>
+          <t>nonconformity_consequences</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>related_risks</t>
+          <t>nonconformity_root_cause</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>applicable_controls</t>
+          <t>nonconformity_similar_check</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>nonconformity_status</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nonconformity_closure_date</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>nonconformity_closure_evidence</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -3764,73 +3388,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>event_datetime</t>
+          <t>responsible_role</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>reporter</t>
+          <t>action_nonconformities</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>event_description</t>
+          <t>action_root_cause</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>affected_assets</t>
+          <t>action_target_date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>initial_assessment</t>
+          <t>action_completion_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>categorized_as_incident</t>
+          <t>action_resources</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>linked_incident</t>
+          <t>action_effectiveness_criteria</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>action_effectiveness_review_date</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>action_effective</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>action_isms_changes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>action_status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -3845,138 +3474,275 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>incident_datetime</t>
+          <t>responsible_role</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>improvement_source</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>improvement_identified_on</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>improvement_identified_by</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>improvement_benefit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>improvement_priority</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>improvement_plan</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>improvement_target_date</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>improvement_completion_date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>improvement_outcome</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>improvement_status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>affected_assets</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>event_occurred_at</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>event_reporter</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>event_assessment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>affected_security_properties</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>incident_category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>incident_severity</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>incident_detection_method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>incident_response_actions</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>incident_containment_actions</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>incident_eradication_actions</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>incident_recovery_actions</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>incident_root_cause</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>incident_lessons_learned</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>incident_evidence</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>incident_notification_required</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>incident_notifications</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>incident_closed_at</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>incident_review</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>affected_assets</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>affected_cia</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>incident_description</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>detection_method</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>response_actions</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>containment_actions</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>eradication_actions</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>recovery_actions</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>root_cause</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>lessons_learned</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>evidence_collected</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>notification_required</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>notifications_made</t>
-        </is>
-      </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>closure_datetime</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>post_incident_review</t>
+          <t>event_occurred_at</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>event_reporter</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>event_assessment</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>isms_id</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"confidentiality,integrity,availability"</formula1>
+    </dataValidation>
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"very_low,low,medium,high,critical"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"confidentiality,integrity,availability"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3989,7 +3755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4005,162 +3771,134 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>commitment_statements</t>
+          <t>policy_commitments</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>applicability_statement</t>
+          <t>policy_applicability</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>communication_date</t>
+          <t>policy_communication_date</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>acknowledgment_required</t>
+          <t>policy_acknowledgement_required</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>last_policy_review_date</t>
+          <t>policy_management_systems</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>next_policy_review_date</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>related_topic_policies</t>
+          <t>title</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>integrated_management_systems</t>
+          <t>description</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>document_reference</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>document_reference</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>author</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>owner</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"iso_iec_27001,iso_iec_27701,iso_iec_27017,iso_iec_27018,iso_iec_42001,iso_9001,iso_14001,iso_22301,iso_iec_20000_1,iso_31000"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
+  <dataValidations count="1">
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"iso_iec_27001,iso_iec_27701,iso_iec_42001,iso_9001,iso_14001,iso_22301,iso_iec_20000_1"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4173,147 +3911,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>topic_area</t>
+          <t>relevant_controls</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>parent_policy</t>
+          <t>topic_policy_topic</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>applicable_controls</t>
+          <t>topic_policy_parent</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>topic_policy_audience</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4324,73 +4047,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>role_type</t>
+          <t>role_category</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>responsibilities</t>
+          <t>role_responsibilities</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>authorities</t>
+          <t>role_authorities</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>accountability</t>
+          <t>role_accountability</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>role_holders</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>delegation_rules</t>
+          <t>role_delegation</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>reporting_line</t>
+          <t>role_reports_to</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -4405,103 +4113,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>responsible_role</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>relevant_controls</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>objective_statement</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>target_value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>current_value</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>metric_definition</t>
+          <t>objective_target</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>measurement_method</t>
+          <t>objective_current_value</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>measurement_frequency</t>
+          <t>objective_metric</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>responsible_role</t>
+          <t>objective_measurement_method</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>target_date</t>
+          <t>objective_measurement_frequency</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>achievement_status</t>
+          <t>objective_target_date</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>related_risks</t>
+          <t>objective_achievement</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>related_controls</t>
+          <t>objective_risks</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>action_plan</t>
+          <t>objective_action_plan</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>objective_resources_required</t>
+          <t>objective_resources</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
           <t>description</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>version</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4527,22 +4220,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>assessment_criteria</t>
+          <t>risk_assessment_criteria</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>assessment_methodology</t>
+          <t>risk_assessment_method</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>likelihood_scale</t>
+          <t>risk_likelihood_scale</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>impact_scale</t>
+          <t>risk_impact_scale</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -4552,131 +4245,116 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>assessment_frequency</t>
+          <t>risk_assessment_frequency</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>trigger_events</t>
+          <t>risk_assessment_triggers</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4687,7 +4365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4703,151 +4381,136 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>assessor</t>
+          <t>assessment_assessor</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>methodology_used</t>
+          <t>assessment_method_used</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>risks_identified</t>
+          <t>assessment_risks</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>summary_findings</t>
+          <t>assessment_summary</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>recommendations</t>
+          <t>assessment_recommendations</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>next_assessment_date</t>
+          <t>assessment_next_date</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>isms_id</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>document_reference</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>approved_by</t>
+          <t>document_version</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>approved_date</t>
+          <t>document_author</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>effective_date</t>
+          <t>document_owner</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>review_date</t>
+          <t>document_approver</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>document_approval_date</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>classification</t>
+          <t>document_effective_date</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>retention_period</t>
+          <t>document_last_review_date</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>distribution_controls</t>
+          <t>document_next_review_date</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>storage_and_preservation</t>
+          <t>document_status</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>change_control_method</t>
+          <t>document_classification</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>external_origin</t>
+          <t>document_retention</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>external_origin_source</t>
+          <t>document_distribution</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>document_storage</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>document_change_control</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>document_external_origin</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>created_date</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>modified_date</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>version</t>
+          <t>document_external_source</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"policy,procedure,standard,guideline,record,plan,report"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>